--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_40_P10.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_40_P10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE4BC09D-98FF-4655-AF99-ECF52653F8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{495F4E84-6BBD-4D12-9765-76F310E436E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,13 +681,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH03,S04aH06,S01aH02,S04aH04,S01aH03,S04aH02,S04aH05,S04aH08,S02aH04,S02aH05,S03aH03,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH04,S02aH02</t>
+    <t>S04aH02,S01aH02,S04aH04,S03aH04,S01aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S02aH02,S03aH03,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S01aH06,S02aH03,S04aH05,S04aH08,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S02aH10,S01aH08,S02aH08,S01aH10,S03aH02,S03aH08,S03aH10,S02aH02,S04aH10,S04aH02,S03aH09,S04aH08,S01aH09,S01aH01,S04aH01,S01aH02,S02aH09,S04aH09,S03aH01</t>
+    <t>S04aH08,S01aH10,S03aH02,S01aH08,S02aH08,S02aH09,S04aH09,S01aH09,S03aH08,S03aH10,S03aH01,S02aH02,S04aH10,S03aH09,S02aH01,S02aH10,S01aH01,S04aH01,S04aH02,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S02aH10,S01aH08,S02aH08,S01aH10,S03aH02,S03aH08,S03aH10,S02aH02,S04aH10,S04aH02,S03aH09,S04aH08,S01aH09,S01aH01,S04aH01,S01aH02,S02aH09,S04aH09,S03aH01</v>
+        <v>S04aH08,S01aH10,S03aH02,S01aH08,S02aH08,S02aH09,S04aH09,S01aH09,S03aH08,S03aH10,S03aH01,S02aH02,S04aH10,S03aH09,S02aH01,S02aH10,S01aH01,S04aH01,S04aH02,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH03,S04aH06,S01aH02,S04aH04,S01aH03,S04aH02,S04aH05,S04aH08,S02aH04,S02aH05,S03aH03,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH04,S02aH02</v>
+        <v>S04aH02,S01aH02,S04aH04,S03aH04,S01aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S02aH02,S03aH03,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S01aH06,S02aH03,S04aH05,S04aH08,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790CFB11-ADC5-432C-98D5-AFEBFA7D77E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA6ACBD-8913-4945-A4C7-D36AE06EEA86}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E36251C3-4AF8-42BA-8A49-0523A6CFE7BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90DCBFCD-F559-49C7-803B-65F639432346}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27210,7 +27210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE20544F-C421-43DF-BA15-B145766F955A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00864899-8547-4B2E-8B3E-E86EF1CF782E}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41663,7 +41663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB64A636-BE02-46EB-A25B-1F0472BF060D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC5A3080-1C34-4894-9CC5-BC3862DC6BC5}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42253,7 +42253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B7419F-2135-425B-BA75-D5AD15F3D91B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34269B9F-F60D-4F54-905D-DE417BA2B707}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43160,7 +43160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFD2727C-2401-4937-B9B5-E11F8CEDBCBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54390D05-3AE9-40BD-A34F-3C5AB8E0E930}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43627,7 +43627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B4865F-4260-4AD0-9CD3-98C556C0D748}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{792029AC-6CC3-4CE3-87EB-326BB10D4FB3}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43673,7 +43673,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="E12" t="s">
         <v>221</v>
@@ -43715,7 +43715,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="E15" t="s">
         <v>221</v>
@@ -43785,7 +43785,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="E20" t="s">
         <v>221</v>
@@ -43799,7 +43799,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="E21" t="s">
         <v>221</v>
@@ -43869,7 +43869,7 @@
         <v>45</v>
       </c>
       <c r="D26">
-        <v>0.19849999999999998</v>
+        <v>0.19850000000000001</v>
       </c>
       <c r="E26" t="s">
         <v>221</v>
@@ -43995,7 +43995,7 @@
         <v>37</v>
       </c>
       <c r="D35">
-        <v>0.31423333333333331</v>
+        <v>0.31423333333333336</v>
       </c>
       <c r="E35" t="s">
         <v>221</v>
@@ -44051,7 +44051,7 @@
         <v>37</v>
       </c>
       <c r="D39">
-        <v>0.29663333333333336</v>
+        <v>0.2966333333333333</v>
       </c>
       <c r="E39" t="s">
         <v>221</v>
@@ -44079,7 +44079,7 @@
         <v>43</v>
       </c>
       <c r="D41">
-        <v>0.21190000000000001</v>
+        <v>0.21189999999999998</v>
       </c>
       <c r="E41" t="s">
         <v>221</v>
@@ -44121,7 +44121,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.33566666666666661</v>
+        <v>0.33566666666666672</v>
       </c>
       <c r="E44" t="s">
         <v>221</v>
@@ -44135,7 +44135,7 @@
         <v>43</v>
       </c>
       <c r="D45">
-        <v>0.22163333333333335</v>
+        <v>0.22163333333333332</v>
       </c>
       <c r="E45" t="s">
         <v>221</v>
@@ -44219,7 +44219,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.31816666666666671</v>
+        <v>0.31816666666666665</v>
       </c>
       <c r="E51" t="s">
         <v>221</v>
@@ -44275,7 +44275,7 @@
         <v>37</v>
       </c>
       <c r="D55">
-        <v>0.2987333333333333</v>
+        <v>0.29873333333333335</v>
       </c>
       <c r="E55" t="s">
         <v>221</v>
@@ -44303,7 +44303,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18930000000000002</v>
+        <v>0.1893</v>
       </c>
       <c r="E57" t="s">
         <v>221</v>
@@ -44443,7 +44443,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.28343333333333331</v>
+        <v>0.28343333333333337</v>
       </c>
       <c r="E67" t="s">
         <v>221</v>
@@ -44513,7 +44513,7 @@
         <v>41</v>
       </c>
       <c r="D72">
-        <v>0.37943333333333329</v>
+        <v>0.37943333333333334</v>
       </c>
       <c r="E72" t="s">
         <v>221</v>
@@ -44569,7 +44569,7 @@
         <v>41</v>
       </c>
       <c r="D76">
-        <v>0.35526666666666662</v>
+        <v>0.35526666666666668</v>
       </c>
       <c r="E76" t="s">
         <v>221</v>
@@ -44611,7 +44611,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.31333333333333335</v>
+        <v>0.3133333333333333</v>
       </c>
       <c r="E79" t="s">
         <v>221</v>
@@ -44737,7 +44737,7 @@
         <v>41</v>
       </c>
       <c r="D88">
-        <v>0.32173333333333332</v>
+        <v>0.32173333333333337</v>
       </c>
       <c r="E88" t="s">
         <v>221</v>
@@ -44807,7 +44807,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.21943333333333337</v>
+        <v>0.21943333333333334</v>
       </c>
       <c r="E93" t="s">
         <v>221</v>
@@ -45003,7 +45003,7 @@
         <v>37</v>
       </c>
       <c r="D107">
-        <v>0.33163333333333334</v>
+        <v>0.33163333333333328</v>
       </c>
       <c r="E107" t="s">
         <v>221</v>
@@ -45031,7 +45031,7 @@
         <v>43</v>
       </c>
       <c r="D109">
-        <v>0.1837333333333333</v>
+        <v>0.18373333333333333</v>
       </c>
       <c r="E109" t="s">
         <v>221</v>
@@ -45045,7 +45045,7 @@
         <v>45</v>
       </c>
       <c r="D110">
-        <v>0.1931333333333333</v>
+        <v>0.19313333333333335</v>
       </c>
       <c r="E110" t="s">
         <v>221</v>
@@ -45059,7 +45059,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.2840333333333333</v>
+        <v>0.28403333333333336</v>
       </c>
       <c r="E111" t="s">
         <v>221</v>
@@ -45087,7 +45087,7 @@
         <v>43</v>
       </c>
       <c r="D113">
-        <v>0.22593333333333335</v>
+        <v>0.22593333333333332</v>
       </c>
       <c r="E113" t="s">
         <v>221</v>
@@ -45101,7 +45101,7 @@
         <v>45</v>
       </c>
       <c r="D114">
-        <v>0.24843333333333331</v>
+        <v>0.24843333333333337</v>
       </c>
       <c r="E114" t="s">
         <v>221</v>
@@ -45143,7 +45143,7 @@
         <v>43</v>
       </c>
       <c r="D117">
-        <v>0.17703333333333329</v>
+        <v>0.17703333333333335</v>
       </c>
       <c r="E117" t="s">
         <v>221</v>
@@ -45171,7 +45171,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.29110000000000003</v>
+        <v>0.29109999999999997</v>
       </c>
       <c r="E119" t="s">
         <v>221</v>
@@ -45199,7 +45199,7 @@
         <v>43</v>
       </c>
       <c r="D121">
-        <v>0.17843333333333336</v>
+        <v>0.17843333333333333</v>
       </c>
       <c r="E121" t="s">
         <v>221</v>
@@ -45227,7 +45227,7 @@
         <v>37</v>
       </c>
       <c r="D123">
-        <v>0.34243333333333337</v>
+        <v>0.34243333333333331</v>
       </c>
       <c r="E123" t="s">
         <v>221</v>
@@ -45241,7 +45241,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.33229999999999998</v>
+        <v>0.33230000000000004</v>
       </c>
       <c r="E124" t="s">
         <v>221</v>
